--- a/data_analysis/rq2_qualitative_ptm.xlsx
+++ b/data_analysis/rq2_qualitative_ptm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pbanyongrakkul/Documents/GitHub/TSE_PTM_Changes/data_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE83563-0AC5-B94D-913E-7431E1FB4943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E5403D-F5BF-D84F-9CF5-0C0CC450E199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="30240" windowHeight="17840" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17840" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="7" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="726">
   <si>
     <t>new seq</t>
   </si>
@@ -1858,21 +1858,6 @@
     <t>Removing unused dependency</t>
   </si>
   <si>
-    <t>He 2021</t>
-  </si>
-  <si>
-    <t>Teyton 2014</t>
-  </si>
-  <si>
-    <t>Kabinna 2016</t>
-  </si>
-  <si>
-    <t>Barbosa 2022</t>
-  </si>
-  <si>
-    <t>Jaisri 2025</t>
-  </si>
-  <si>
     <t>E1</t>
   </si>
   <si>
@@ -1888,9 +1873,6 @@
     <t>E5</t>
   </si>
   <si>
-    <t>E1, E4</t>
-  </si>
-  <si>
     <t>D1</t>
   </si>
   <si>
@@ -1985,12 +1967,6 @@
   </si>
   <si>
     <t>A14</t>
-  </si>
-  <si>
-    <t>C2*</t>
-  </si>
-  <si>
-    <t>Our deps</t>
   </si>
   <si>
     <t xml:space="preserve"> Storage requirement and runtime dependency overhead</t>
@@ -2087,57 +2063,6 @@
   </si>
   <si>
     <t>Remove unnecessary or unused dependency</t>
-  </si>
-  <si>
-    <t>D3*</t>
-  </si>
-  <si>
-    <t>DT4</t>
-  </si>
-  <si>
-    <t>A7, A6*</t>
-  </si>
-  <si>
-    <t>B1*, B3*</t>
-  </si>
-  <si>
-    <t>B1, B4*</t>
-  </si>
-  <si>
-    <t>D2*</t>
-  </si>
-  <si>
-    <t>DT2</t>
-  </si>
-  <si>
-    <t>E5*</t>
-  </si>
-  <si>
-    <t>DT5</t>
-  </si>
-  <si>
-    <t>A10, A11*</t>
-  </si>
-  <si>
-    <t>B4*</t>
-  </si>
-  <si>
-    <t>DT6</t>
-  </si>
-  <si>
-    <t>A5-</t>
-  </si>
-  <si>
-    <t>B2-</t>
-  </si>
-  <si>
-    <t>DT5*</t>
-  </si>
-  <si>
-    <t>C4-</t>
-  </si>
-  <si>
-    <t>DT1-</t>
   </si>
   <si>
     <t>Latex ID</t>
@@ -2293,12 +2218,6 @@
     </r>
   </si>
   <si>
-    <t>Bavota 2015</t>
-  </si>
-  <si>
-    <t>F3-</t>
-  </si>
-  <si>
     <t>Need to add or extend NLP capabilities (e.g., extraction, classification, generation, speech/text processing)</t>
   </si>
   <si>
@@ -2414,6 +2333,42 @@
   </si>
   <si>
     <t>Code Comment with Rationale</t>
+  </si>
+  <si>
+    <t>discussed in prior</t>
+  </si>
+  <si>
+    <t>partially discussed in prior</t>
+  </si>
+  <si>
+    <t>discussed in our libs</t>
+  </si>
+  <si>
+    <t>partially discussed in our libs</t>
+  </si>
+  <si>
+    <t>Insufficient PTM evaluation and testing safeguards</t>
+  </si>
+  <si>
+    <t>PTM deprecation and functionality retirement decisions</t>
+  </si>
+  <si>
+    <t>Lack of lightweight, PTM-based functional testing</t>
+  </si>
+  <si>
+    <t>Need for PTM development and optimization functionality</t>
+  </si>
+  <si>
+    <t>User-requested PTM or feature support</t>
+  </si>
+  <si>
+    <t>Lack of PTM evaluation or benchmark</t>
+  </si>
+  <si>
+    <t>Inconsistent or poor PTM output quality</t>
+  </si>
+  <si>
+    <t>Upstream PTM and dependency update</t>
   </si>
 </sst>
 </file>
@@ -2423,9 +2378,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2574,63 +2536,70 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2647,6 +2616,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2981,7 +2967,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>727</v>
+        <v>700</v>
       </c>
       <c r="B4" cm="1">
         <f t="array" ref="B4">SUMPRODUCT(
@@ -3010,7 +2996,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="B7">
         <f>COUNT(_xlfn.UNIQUE('key information'!A2:A220))</f>
@@ -3069,10 +3055,10 @@
         <v>483</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>729</v>
+        <v>702</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>730</v>
+        <v>703</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -3092,7 +3078,7 @@
         <v>541</v>
       </c>
       <c r="J14" t="s">
-        <v>727</v>
+        <v>700</v>
       </c>
       <c r="K14">
         <f>B4</f>
@@ -3125,7 +3111,7 @@
         <v>38.638163103721297</v>
       </c>
       <c r="J15" t="s">
-        <v>731</v>
+        <v>704</v>
       </c>
       <c r="K15" cm="1">
         <f t="array" ref="K15">SUMPRODUCT(
@@ -3174,7 +3160,7 @@
         <v>16.806722689075631</v>
       </c>
       <c r="J16" t="s">
-        <v>732</v>
+        <v>705</v>
       </c>
       <c r="K16" cm="1">
         <f t="array" ref="K16">SUMPRODUCT(
@@ -3223,7 +3209,7 @@
         <v>75</v>
       </c>
       <c r="J17" t="s">
-        <v>733</v>
+        <v>706</v>
       </c>
       <c r="K17" cm="1">
         <f t="array" ref="K17">SUMPRODUCT(
@@ -3258,7 +3244,7 @@
         <v>491</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>734</v>
+        <v>707</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -3271,7 +3257,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="E20" t="s">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="F20">
         <f>B7</f>
@@ -3290,7 +3276,7 @@
         <v>41.247002398081534</v>
       </c>
       <c r="E21" t="s">
-        <v>735</v>
+        <v>708</v>
       </c>
       <c r="F21">
         <v>74</v>
@@ -3316,7 +3302,7 @@
         <v>29.016786570743403</v>
       </c>
       <c r="E22" t="s">
-        <v>736</v>
+        <v>709</v>
       </c>
       <c r="F22">
         <v>65</v>
@@ -3342,7 +3328,7 @@
         <v>17.026378896882495</v>
       </c>
       <c r="E23" t="s">
-        <v>737</v>
+        <v>710</v>
       </c>
       <c r="F23">
         <v>34</v>
@@ -3368,7 +3354,7 @@
         <v>4.5563549160671464</v>
       </c>
       <c r="E24" t="s">
-        <v>738</v>
+        <v>711</v>
       </c>
       <c r="F24">
         <v>13</v>
@@ -3394,7 +3380,7 @@
         <v>4.5563549160671464</v>
       </c>
       <c r="E25" t="s">
-        <v>739</v>
+        <v>712</v>
       </c>
       <c r="F25">
         <v>12</v>
@@ -3420,7 +3406,7 @@
         <v>3.5971223021582732</v>
       </c>
       <c r="E26" t="s">
-        <v>740</v>
+        <v>713</v>
       </c>
       <c r="F26">
         <v>11</v>
@@ -3459,9 +3445,9 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>603</v>
-      </c>
-      <c r="B2" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>585</v>
       </c>
       <c r="C2" t="s">
@@ -3470,81 +3456,81 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>604</v>
-      </c>
-      <c r="B3" s="21"/>
+        <v>598</v>
+      </c>
+      <c r="B3" s="23"/>
       <c r="C3" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>605</v>
-      </c>
-      <c r="B4" s="21"/>
+        <v>599</v>
+      </c>
+      <c r="B4" s="23"/>
       <c r="C4" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>606</v>
-      </c>
-      <c r="B5" s="21"/>
+        <v>600</v>
+      </c>
+      <c r="B5" s="23"/>
       <c r="C5" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>607</v>
-      </c>
-      <c r="B6" s="21"/>
+        <v>601</v>
+      </c>
+      <c r="B6" s="23"/>
       <c r="C6" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>608</v>
-      </c>
-      <c r="B7" s="21"/>
+        <v>602</v>
+      </c>
+      <c r="B7" s="23"/>
       <c r="C7" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>609</v>
-      </c>
-      <c r="B8" s="21"/>
+        <v>603</v>
+      </c>
+      <c r="B8" s="23"/>
       <c r="C8" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>610</v>
-      </c>
-      <c r="B9" s="21"/>
+        <v>604</v>
+      </c>
+      <c r="B9" s="23"/>
       <c r="C9" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>611</v>
-      </c>
-      <c r="B10" s="21"/>
+        <v>605</v>
+      </c>
+      <c r="B10" s="23"/>
       <c r="C10" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>612</v>
-      </c>
-      <c r="B11" s="21" t="s">
+        <v>606</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>586</v>
       </c>
       <c r="C11" t="s">
@@ -3553,27 +3539,27 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>613</v>
-      </c>
-      <c r="B12" s="21"/>
+        <v>607</v>
+      </c>
+      <c r="B12" s="23"/>
       <c r="C12" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>614</v>
-      </c>
-      <c r="B13" s="21"/>
+        <v>608</v>
+      </c>
+      <c r="B13" s="23"/>
       <c r="C13" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>615</v>
-      </c>
-      <c r="B14" s="21"/>
+        <v>609</v>
+      </c>
+      <c r="B14" s="23"/>
       <c r="C14" t="s">
         <v>584</v>
       </c>
@@ -3583,7 +3569,7 @@
     <mergeCell ref="B2:B10"/>
     <mergeCell ref="B11:B14"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -3602,66 +3588,66 @@
         <v>279</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B2" t="s">
         <v>587</v>
       </c>
       <c r="C2" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B3" t="s">
         <v>588</v>
       </c>
       <c r="C3" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B4" t="s">
         <v>589</v>
       </c>
       <c r="C4" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B5" t="s">
         <v>590</v>
       </c>
       <c r="C5" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B6" t="s">
         <v>591</v>
       </c>
       <c r="C6" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -3676,67 +3662,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="22"/>
-      <c r="B1" s="22" t="s">
+      <c r="A1" s="17"/>
+      <c r="B1" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>638</v>
+      <c r="C1" s="17" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>686</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>695</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>691</v>
+      <c r="A2" s="18" t="s">
+        <v>661</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>670</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
-        <v>687</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>696</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>692</v>
+      <c r="A3" s="18" t="s">
+        <v>662</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>671</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
-        <v>688</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>697</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>693</v>
+      <c r="A4" s="18" t="s">
+        <v>663</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>672</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
-        <v>689</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>698</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>694</v>
+      <c r="A5" s="18" t="s">
+        <v>664</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>690</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>699</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>685</v>
+      <c r="A6" s="18" t="s">
+        <v>665</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>674</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -6973,7 +6959,7 @@
         <v>timm/vit_so400m_patch14_siglip_384.webli</v>
       </c>
       <c r="I34" t="str">
-        <f t="shared" ref="I34:I65" si="8">B34 &amp; "||" &amp; F34 &amp; "||" &amp; H34</f>
+        <f t="shared" ref="I34:I63" si="8">B34 &amp; "||" &amp; F34 &amp; "||" &amp; H34</f>
         <v>61||['add']||timm/vit_so400m_patch14_siglip_384.webli</v>
       </c>
       <c r="J34">
@@ -13084,7 +13070,7 @@
         <v>google-bert/bert-base-uncased</v>
       </c>
       <c r="I97" t="str">
-        <f t="shared" ref="I97:I128" si="17">B97 &amp; "||" &amp; F97 &amp; "||" &amp; H97</f>
+        <f t="shared" ref="I97:I119" si="17">B97 &amp; "||" &amp; F97 &amp; "||" &amp; H97</f>
         <v>155||['add']||google-bert/bert-base-uncased</v>
       </c>
       <c r="J97">
@@ -24724,7 +24710,7 @@
         <v>followumesh/granite-3b-lora8-bias</v>
       </c>
       <c r="I217" t="str">
-        <f t="shared" ref="I217:I248" si="35">B217 &amp; "||" &amp; F217 &amp; "||" &amp; H217</f>
+        <f t="shared" ref="I217:I220" si="35">B217 &amp; "||" &amp; F217 &amp; "||" &amp; H217</f>
         <v>204||['remove']||followumesh/granite-3b-lora8-bias</v>
       </c>
       <c r="J217">
@@ -29315,7 +29301,7 @@
         <v>528</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>446</v>
@@ -29368,7 +29354,7 @@
         <v>368</v>
       </c>
       <c r="C2" t="s">
-        <v>702</v>
+        <v>675</v>
       </c>
       <c r="D2">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A2)</f>
@@ -29453,7 +29439,7 @@
         <v>542</v>
       </c>
       <c r="C3" t="s">
-        <v>703</v>
+        <v>676</v>
       </c>
       <c r="D3">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A3)</f>
@@ -29538,7 +29524,7 @@
         <v>369</v>
       </c>
       <c r="C4" t="s">
-        <v>704</v>
+        <v>677</v>
       </c>
       <c r="D4">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A4)</f>
@@ -29623,7 +29609,7 @@
         <v>518</v>
       </c>
       <c r="C5" t="s">
-        <v>705</v>
+        <v>678</v>
       </c>
       <c r="D5">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A5)</f>
@@ -29708,7 +29694,7 @@
         <v>372</v>
       </c>
       <c r="C6" t="s">
-        <v>706</v>
+        <v>679</v>
       </c>
       <c r="D6">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A6)</f>
@@ -29790,10 +29776,10 @@
         <v>383</v>
       </c>
       <c r="B7" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="C7" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="D7">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A7)</f>
@@ -29878,7 +29864,7 @@
         <v>504</v>
       </c>
       <c r="C8" t="s">
-        <v>707</v>
+        <v>680</v>
       </c>
       <c r="D8">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A8)</f>
@@ -29963,7 +29949,7 @@
         <v>373</v>
       </c>
       <c r="C9" t="s">
-        <v>708</v>
+        <v>681</v>
       </c>
       <c r="D9">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A9)</f>
@@ -30048,7 +30034,7 @@
         <v>541</v>
       </c>
       <c r="C10" t="s">
-        <v>715</v>
+        <v>688</v>
       </c>
       <c r="D10">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A10)</f>
@@ -30133,7 +30119,7 @@
         <v>463</v>
       </c>
       <c r="C11" t="s">
-        <v>709</v>
+        <v>682</v>
       </c>
       <c r="D11">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A11)</f>
@@ -30218,7 +30204,7 @@
         <v>371</v>
       </c>
       <c r="C12" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
       <c r="D12">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A12)</f>
@@ -30303,7 +30289,7 @@
         <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>717</v>
+        <v>690</v>
       </c>
       <c r="D13">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A13)</f>
@@ -30388,7 +30374,7 @@
         <v>457</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>718</v>
+        <v>691</v>
       </c>
       <c r="D14">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A14)</f>
@@ -30473,7 +30459,7 @@
         <v>460</v>
       </c>
       <c r="C15" t="s">
-        <v>719</v>
+        <v>692</v>
       </c>
       <c r="D15">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A15)</f>
@@ -30558,7 +30544,7 @@
         <v>519</v>
       </c>
       <c r="C16" t="s">
-        <v>720</v>
+        <v>693</v>
       </c>
       <c r="D16">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A16)</f>
@@ -30643,7 +30629,7 @@
         <v>458</v>
       </c>
       <c r="C17" t="s">
-        <v>710</v>
+        <v>683</v>
       </c>
       <c r="D17">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A17)</f>
@@ -30728,7 +30714,7 @@
         <v>501</v>
       </c>
       <c r="C18" t="s">
-        <v>711</v>
+        <v>684</v>
       </c>
       <c r="D18">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A18)</f>
@@ -30813,7 +30799,7 @@
         <v>529</v>
       </c>
       <c r="C19" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="D19">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A19)</f>
@@ -30898,7 +30884,7 @@
         <v>370</v>
       </c>
       <c r="C20" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="D20">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A20)</f>
@@ -30983,7 +30969,7 @@
         <v>517</v>
       </c>
       <c r="C21" t="s">
-        <v>721</v>
+        <v>694</v>
       </c>
       <c r="D21">
         <f>COUNTIF(codes!F:F, 'sub-themes'!A21)</f>
@@ -31096,13 +31082,13 @@
         <v>278</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>684</v>
+        <v>659</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>279</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>531</v>
@@ -31155,7 +31141,7 @@
         <v>467</v>
       </c>
       <c r="D2" t="s">
-        <v>722</v>
+        <v>695</v>
       </c>
       <c r="E2" cm="1">
         <f t="array" ref="E2">SUMPRODUCT(--ISNUMBER(SEARCH(","&amp;$A2&amp;",", ","&amp;'sub-themes'!$H:$H&amp;",")))</f>
@@ -31250,7 +31236,7 @@
         <v>466</v>
       </c>
       <c r="D3" t="s">
-        <v>723</v>
+        <v>696</v>
       </c>
       <c r="E3" cm="1">
         <f t="array" ref="E3">SUMPRODUCT(--ISNUMBER(SEARCH(","&amp;$A3&amp;",", ","&amp;'sub-themes'!$H:$H&amp;",")))</f>
@@ -31345,7 +31331,7 @@
         <v>527</v>
       </c>
       <c r="D4" t="s">
-        <v>724</v>
+        <v>697</v>
       </c>
       <c r="E4" cm="1">
         <f t="array" ref="E4">SUMPRODUCT(--ISNUMBER(SEARCH(","&amp;$A4&amp;",", ","&amp;'sub-themes'!$H:$H&amp;",")))</f>
@@ -31440,7 +31426,7 @@
         <v>540</v>
       </c>
       <c r="D5" t="s">
-        <v>725</v>
+        <v>698</v>
       </c>
       <c r="E5" cm="1">
         <f t="array" ref="E5">SUMPRODUCT(--ISNUMBER(SEARCH(","&amp;$A5&amp;",", ","&amp;'sub-themes'!$H:$H&amp;",")))</f>
@@ -31535,7 +31521,7 @@
         <v>465</v>
       </c>
       <c r="D6" t="s">
-        <v>726</v>
+        <v>699</v>
       </c>
       <c r="E6" cm="1">
         <f t="array" ref="E6">SUMPRODUCT(--ISNUMBER(SEARCH(","&amp;$A6&amp;",", ","&amp;'sub-themes'!$H:$H&amp;",")))</f>
@@ -31652,15 +31638,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE64544-59EB-4346-962F-35D35E3788D0}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.6640625" customWidth="1"/>
     <col min="2" max="2" width="5.1640625" customWidth="1"/>
     <col min="3" max="3" width="47.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>279</v>
       </c>
@@ -31668,29 +31658,20 @@
         <v>528</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>592</v>
+        <v>714</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>593</v>
+        <v>715</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>594</v>
+        <v>716</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>595</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>596</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>700</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
         <v>467</v>
       </c>
       <c r="B2" t="s">
@@ -31699,121 +31680,106 @@
       <c r="C2" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="D2" t="s">
-        <v>679</v>
-      </c>
-      <c r="E2" t="s">
-        <v>680</v>
-      </c>
-      <c r="F2" t="s">
-        <v>682</v>
-      </c>
-      <c r="I2" t="s">
-        <v>701</v>
-      </c>
-      <c r="J2" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
+      <c r="D2" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="20"/>
       <c r="B3" t="s">
         <v>379</v>
       </c>
       <c r="C3" t="s">
         <v>368</v>
       </c>
-      <c r="D3" t="s">
-        <v>679</v>
-      </c>
-      <c r="E3" t="s">
-        <v>680</v>
-      </c>
-      <c r="F3" t="s">
-        <v>682</v>
-      </c>
-      <c r="I3" t="s">
-        <v>701</v>
-      </c>
-      <c r="J3" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
+      <c r="D3" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" s="24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="20"/>
       <c r="B4" t="s">
         <v>393</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D4" t="s">
-        <v>679</v>
-      </c>
-      <c r="E4" t="s">
-        <v>680</v>
-      </c>
-      <c r="F4" t="s">
-        <v>682</v>
-      </c>
-      <c r="I4" t="s">
-        <v>701</v>
-      </c>
-      <c r="J4" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="18"/>
+        <v>721</v>
+      </c>
+      <c r="D4" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="20"/>
       <c r="B5" t="s">
         <v>388</v>
       </c>
       <c r="C5" t="s">
         <v>371</v>
       </c>
-      <c r="D5" t="s">
-        <v>679</v>
-      </c>
-      <c r="E5" t="s">
-        <v>680</v>
-      </c>
-      <c r="F5" t="s">
-        <v>682</v>
-      </c>
-      <c r="I5" t="s">
-        <v>701</v>
-      </c>
-      <c r="J5" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="18"/>
+      <c r="D5" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="20"/>
       <c r="B6" t="s">
         <v>392</v>
       </c>
       <c r="C6" t="s">
-        <v>529</v>
-      </c>
-      <c r="D6" t="s">
-        <v>679</v>
-      </c>
-      <c r="E6" t="s">
-        <v>680</v>
-      </c>
-      <c r="F6" t="s">
-        <v>682</v>
-      </c>
-      <c r="I6" t="s">
-        <v>701</v>
-      </c>
-      <c r="J6" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
-        <v>527</v>
+        <v>722</v>
+      </c>
+      <c r="D6" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="21" t="s">
+        <v>718</v>
       </c>
       <c r="B7" t="s">
         <v>456</v>
@@ -31821,48 +31787,105 @@
       <c r="C7" s="14" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
+      <c r="D7" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="22"/>
       <c r="B8" t="s">
         <v>386</v>
       </c>
       <c r="C8" t="s">
-        <v>541</v>
-      </c>
-      <c r="G8" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
+        <v>720</v>
+      </c>
+      <c r="D8" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="22"/>
       <c r="B9" t="s">
         <v>385</v>
       </c>
       <c r="C9" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
+        <v>723</v>
+      </c>
+      <c r="D9" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="22"/>
       <c r="B10" t="s">
         <v>464</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
+        <v>724</v>
+      </c>
+      <c r="D10" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="22"/>
       <c r="B11" t="s">
         <v>389</v>
       </c>
       <c r="C11" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
+      <c r="D11" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="19" t="s">
         <v>465</v>
       </c>
       <c r="B12" t="s">
@@ -31871,42 +31894,63 @@
       <c r="C12" s="13" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
+      <c r="D12" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
       <c r="B13" t="s">
         <v>387</v>
       </c>
       <c r="C13" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
+      <c r="D13" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="20"/>
       <c r="B14" t="s">
         <v>383</v>
       </c>
       <c r="C14" t="s">
         <v>510</v>
       </c>
-      <c r="D14" t="s">
-        <v>669</v>
-      </c>
-      <c r="E14" t="s">
-        <v>670</v>
-      </c>
-      <c r="F14" t="s">
-        <v>635</v>
-      </c>
-      <c r="H14" t="s">
-        <v>602</v>
-      </c>
-      <c r="J14" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="17" t="s">
+      <c r="D14" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="19" t="s">
         <v>540</v>
       </c>
       <c r="B15" t="s">
@@ -31915,84 +31959,84 @@
       <c r="C15" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="D15" t="s">
-        <v>631</v>
-      </c>
-      <c r="E15" t="s">
-        <v>671</v>
-      </c>
-      <c r="F15" t="s">
-        <v>291</v>
-      </c>
-      <c r="G15" t="s">
-        <v>672</v>
-      </c>
-      <c r="I15" t="s">
-        <v>687</v>
-      </c>
-      <c r="J15" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
+      <c r="D15" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="20"/>
       <c r="B16" t="s">
         <v>394</v>
       </c>
       <c r="C16" t="s">
-        <v>517</v>
-      </c>
-      <c r="H16" t="s">
-        <v>674</v>
-      </c>
-      <c r="J16" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
+        <v>719</v>
+      </c>
+      <c r="D16" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="20"/>
       <c r="B17" t="s">
         <v>448</v>
       </c>
       <c r="C17" t="s">
-        <v>518</v>
-      </c>
-      <c r="D17" t="s">
-        <v>676</v>
-      </c>
-      <c r="E17" t="s">
-        <v>677</v>
-      </c>
-      <c r="F17" t="s">
-        <v>291</v>
-      </c>
-      <c r="I17" t="s">
-        <v>689</v>
-      </c>
-      <c r="J17" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
+        <v>725</v>
+      </c>
+      <c r="D17" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="20"/>
       <c r="B18" t="s">
         <v>384</v>
       </c>
       <c r="C18" t="s">
         <v>504</v>
       </c>
-      <c r="D18" t="s">
-        <v>633</v>
-      </c>
-      <c r="I18" t="s">
-        <v>690</v>
-      </c>
-      <c r="J18" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
+      <c r="D18" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="19" t="s">
         <v>466</v>
       </c>
       <c r="B19" t="s">
@@ -32001,59 +32045,59 @@
       <c r="C19" s="15" t="s">
         <v>542</v>
       </c>
-      <c r="D19" t="s">
-        <v>679</v>
-      </c>
-      <c r="E19" t="s">
-        <v>680</v>
-      </c>
-      <c r="F19" t="s">
-        <v>682</v>
-      </c>
-      <c r="J19" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
+      <c r="D19" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="20"/>
       <c r="B20" t="s">
         <v>390</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D20" t="s">
-        <v>679</v>
-      </c>
-      <c r="E20" t="s">
-        <v>680</v>
-      </c>
-      <c r="F20" t="s">
-        <v>682</v>
-      </c>
-      <c r="J20" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
+      <c r="D20" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="20"/>
       <c r="B21" t="s">
         <v>459</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D21" t="s">
-        <v>679</v>
-      </c>
-      <c r="E21" t="s">
-        <v>680</v>
-      </c>
-      <c r="F21" t="s">
-        <v>682</v>
-      </c>
-      <c r="J21" t="s">
-        <v>683</v>
+      <c r="D21" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="24" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -32064,7 +32108,7 @@
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A19:A21"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -32088,178 +32132,178 @@
         <v>528</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>621</v>
-      </c>
-      <c r="B2" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>545</v>
       </c>
       <c r="C2" t="s">
         <v>548</v>
       </c>
       <c r="D2" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>622</v>
-      </c>
-      <c r="B3" s="21"/>
+        <v>616</v>
+      </c>
+      <c r="B3" s="23"/>
       <c r="C3" t="s">
         <v>546</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>623</v>
-      </c>
-      <c r="B4" s="21"/>
+        <v>617</v>
+      </c>
+      <c r="B4" s="23"/>
       <c r="C4" s="2" t="s">
         <v>547</v>
       </c>
       <c r="D4" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>624</v>
-      </c>
-      <c r="B5" s="21" t="s">
+        <v>618</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>549</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>550</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>625</v>
-      </c>
-      <c r="B6" s="21"/>
+        <v>619</v>
+      </c>
+      <c r="B6" s="23"/>
       <c r="C6" s="2" t="s">
         <v>551</v>
       </c>
       <c r="D6" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>626</v>
-      </c>
-      <c r="B7" s="21"/>
+        <v>620</v>
+      </c>
+      <c r="B7" s="23"/>
       <c r="C7" s="2" t="s">
         <v>552</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>627</v>
-      </c>
-      <c r="B8" s="21"/>
+        <v>621</v>
+      </c>
+      <c r="B8" s="23"/>
       <c r="C8" s="2" t="s">
         <v>553</v>
       </c>
       <c r="D8" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>628</v>
-      </c>
-      <c r="B9" s="21"/>
+        <v>622</v>
+      </c>
+      <c r="B9" s="23"/>
       <c r="C9" s="2" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>629</v>
-      </c>
-      <c r="B10" s="21"/>
+        <v>623</v>
+      </c>
+      <c r="B10" s="23"/>
       <c r="C10" s="2" t="s">
         <v>555</v>
       </c>
       <c r="D10" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>630</v>
-      </c>
-      <c r="B11" s="21"/>
+        <v>624</v>
+      </c>
+      <c r="B11" s="23"/>
       <c r="C11" s="2" t="s">
         <v>556</v>
       </c>
       <c r="D11" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>631</v>
-      </c>
-      <c r="B12" s="21" t="s">
+        <v>625</v>
+      </c>
+      <c r="B12" s="23" t="s">
         <v>557</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>558</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="80" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>632</v>
-      </c>
-      <c r="B13" s="21"/>
+        <v>626</v>
+      </c>
+      <c r="B13" s="23"/>
       <c r="C13" s="2" t="s">
         <v>560</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>633</v>
-      </c>
-      <c r="B14" s="21"/>
+        <v>627</v>
+      </c>
+      <c r="B14" s="23"/>
       <c r="C14" s="2" t="s">
         <v>559</v>
       </c>
       <c r="D14" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>634</v>
-      </c>
-      <c r="B15" s="21"/>
+        <v>628</v>
+      </c>
+      <c r="B15" s="23"/>
       <c r="C15" s="2" t="s">
         <v>561</v>
       </c>
       <c r="D15" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -32268,7 +32312,7 @@
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -32286,66 +32330,66 @@
         <v>279</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="96" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B2" t="s">
         <v>562</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B3" t="s">
         <v>563</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B4" t="s">
         <v>564</v>
       </c>
       <c r="C4" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B5" t="s">
         <v>565</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="B6" t="s">
         <v>566</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -32364,7 +32408,7 @@
         <v>279</v>
       </c>
       <c r="C1" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -32375,7 +32419,7 @@
         <v>567</v>
       </c>
       <c r="C2" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -32386,7 +32430,7 @@
         <v>568</v>
       </c>
       <c r="C3" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="112" x14ac:dyDescent="0.2">
@@ -32397,7 +32441,7 @@
         <v>569</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -32408,7 +32452,7 @@
         <v>570</v>
       </c>
       <c r="C5" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -32419,11 +32463,11 @@
         <v>571</v>
       </c>
       <c r="C6" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
